--- a/backend/src/svr_backend/excel/templates/trial_balance_template.xlsx
+++ b/backend/src/svr_backend/excel/templates/trial_balance_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="609" firstSheet="316" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="609" firstSheet="316" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="SEP12" sheetId="1" state="visible" r:id="rId1"/>
@@ -4711,7 +4711,7 @@
     <row r="20" customFormat="1" s="19">
       <c r="A20" s="798" t="inlineStr">
         <is>
-          <t>2T/1.40 ML Total #</t>
+          <t>2T/2.40 ML Total#</t>
         </is>
       </c>
       <c r="B20" s="799" t="n">
